--- a/business_forms/030_idea_backlog_form--business_forms.xlsx
+++ b/business_forms/030_idea_backlog_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1146,8 +1146,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe', 'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_smith',_'value':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Smith', 'value': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe', 'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_smith',_'value':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Smith', 'value': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe', 'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_smith',_'value':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Smith', 'value': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
